--- a/data/crops/lu_c_factor_inventory.xlsx
+++ b/data/crops/lu_c_factor_inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE3B18A-B01B-4791-895C-7BFAF4541078}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{222691F9-9D3B-4F39-9C0E-A780B282291D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F9D02B0-B27B-4DAB-8C90-F4F799F4886A}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="487">
   <si>
     <t>file_name</t>
   </si>
@@ -1329,102 +1329,12 @@
     <t>../data/land_use/lu_Irrigated_Apples.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Bananas.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Cabbages.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Carrots.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Cocoa.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Coconuts.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Coffee.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_cotton.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Irrigated_Grapes.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Groundnuts.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Oil_palm.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Olives.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Onions.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Oranges.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Potatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Irrigated_Rice.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Soybeans.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sugarbeet.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sugarcane.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sunflower.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sweet_potatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Tobacco.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Tomatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Needleleaf_Evergreen_Boreal_dry.tif</t>
   </si>
   <si>
@@ -1449,93 +1359,12 @@
     <t>../data/land_use/lu_Rainfed_Apples.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Bananas.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Cocoa.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Coconuts.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Coffee.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_cotton.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Rainfed_Grapes.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Groundnuts.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Oil_palm.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Olives.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Oranges.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Potatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Rainfed_Rice.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Soybeans.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sugarbeet.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sugarcane.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sunflower.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sweet_potatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Tobacco.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Tomatoes.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>../data/land_use/lu_Urban.tif</t>
   </si>
   <si>
@@ -1552,6 +1381,165 @@
   </si>
   <si>
     <t>annual</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cabbage_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Carrot_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cotton_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Onion_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Potato_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sugar beet_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sweet potato_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Tobacco_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Tomato_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_rf_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cotton_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Potato_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sugar beet_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sweet potato_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Tobacco_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Tomato_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_rf_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Groundnut_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Groundnut_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Banana_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cocoa_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Coconut_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Coffee_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Oil palm_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Olive_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Orange_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sugarcane_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Banana_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cocoa_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Coconut_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Coffee_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Oil palm_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Olive_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Orange_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sugarcane_rf.tif</t>
   </si>
 </sst>
 </file>
@@ -1685,7 +1673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1713,6 +1701,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1839,13 +1830,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}" name="foreground_occupation_file_index" displayName="foreground_occupation_file_index" ref="A1:M81" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Wheat"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{705AD7F1-810F-4078-AF9D-E2A5540C1883}" uniqueName="1" name="file_name" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{058DBECE-D8A6-44ED-99FF-D660796ED3BB}" uniqueName="2" name="land_use" queryTableFieldId="2" dataDxfId="9"/>
@@ -2189,7 +2174,7 @@
   <cols>
     <col min="1" max="1" width="28.1796875" customWidth="1"/>
     <col min="2" max="2" width="44.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" customWidth="1"/>
     <col min="4" max="4" width="38.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
@@ -2219,16 +2204,16 @@
         <v>89</v>
       </c>
       <c r="G1" t="s">
-        <v>486</v>
+        <v>429</v>
       </c>
       <c r="H1" t="s">
         <v>306</v>
       </c>
       <c r="I1" t="s">
-        <v>487</v>
+        <v>430</v>
       </c>
       <c r="J1" t="s">
-        <v>488</v>
+        <v>431</v>
       </c>
       <c r="K1" t="s">
         <v>315</v>
@@ -2240,7 +2225,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -2279,7 +2264,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -2318,7 +2303,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -2357,7 +2342,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>327</v>
       </c>
@@ -2396,7 +2381,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>328</v>
       </c>
@@ -2435,7 +2420,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>329</v>
       </c>
@@ -2474,7 +2459,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>330</v>
       </c>
@@ -2513,7 +2498,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>331</v>
       </c>
@@ -2552,7 +2537,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>332</v>
       </c>
@@ -2591,7 +2576,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>333</v>
       </c>
@@ -2615,7 +2600,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H11" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I11" t="s">
         <v>307</v>
@@ -2634,15 +2619,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>334</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>416</v>
+      <c r="C12" s="11" t="s">
+        <v>471</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -2658,7 +2643,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H12" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I12" t="s">
         <v>307</v>
@@ -2677,15 +2662,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>335</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>417</v>
+      <c r="C13" s="11" t="s">
+        <v>434</v>
       </c>
       <c r="D13" t="s">
         <v>127</v>
@@ -2701,7 +2686,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H13" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I13" t="s">
         <v>308</v>
@@ -2721,15 +2706,15 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>336</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>418</v>
+      <c r="C14" s="11" t="s">
+        <v>435</v>
       </c>
       <c r="D14" t="s">
         <v>127</v>
@@ -2745,7 +2730,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H14" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I14" t="s">
         <v>308</v>
@@ -2764,15 +2749,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>337</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>419</v>
+      <c r="C15" s="11" t="s">
+        <v>436</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2788,7 +2773,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H15" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I15" t="s">
         <v>309</v>
@@ -2807,15 +2792,15 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>338</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>420</v>
+      <c r="C16" s="11" t="s">
+        <v>437</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -2831,7 +2816,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H16" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I16" t="s">
         <v>310</v>
@@ -2850,15 +2835,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>339</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>421</v>
+      <c r="C17" s="11" t="s">
+        <v>472</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2874,7 +2859,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H17" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I17" t="s">
         <v>307</v>
@@ -2893,15 +2878,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>340</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>422</v>
+      <c r="C18" s="11" t="s">
+        <v>473</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -2917,7 +2902,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H18" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I18" t="s">
         <v>307</v>
@@ -2936,15 +2921,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>341</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>423</v>
+      <c r="C19" s="11" t="s">
+        <v>474</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -2960,7 +2945,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H19" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I19" t="s">
         <v>98</v>
@@ -2979,15 +2964,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>342</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>424</v>
+      <c r="C20" s="11" t="s">
+        <v>438</v>
       </c>
       <c r="D20" t="s">
         <v>311</v>
@@ -3003,7 +2988,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H20" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I20" t="s">
         <v>311</v>
@@ -3022,7 +3007,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>343</v>
       </c>
@@ -3030,7 +3015,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D21" t="s">
         <v>100</v>
@@ -3046,7 +3031,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H21" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I21" t="s">
         <v>313</v>
@@ -3065,15 +3050,15 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>344</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>426</v>
+      <c r="C22" s="11" t="s">
+        <v>468</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -3089,7 +3074,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H22" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I22" t="s">
         <v>314</v>
@@ -3108,15 +3093,15 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>345</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>427</v>
+      <c r="C23" s="11" t="s">
+        <v>439</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -3132,7 +3117,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H23" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I23" t="s">
         <v>308</v>
@@ -3152,15 +3137,15 @@
         <v>0.33440000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>346</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>428</v>
+      <c r="C24" s="11" t="s">
+        <v>440</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -3176,7 +3161,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H24" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I24" t="s">
         <v>308</v>
@@ -3195,15 +3180,15 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>347</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>429</v>
+      <c r="C25" s="11" t="s">
+        <v>475</v>
       </c>
       <c r="D25" t="s">
         <v>102</v>
@@ -3219,7 +3204,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H25" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I25" t="s">
         <v>307</v>
@@ -3238,15 +3223,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>348</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>430</v>
+      <c r="C26" s="11" t="s">
+        <v>476</v>
       </c>
       <c r="D26" t="s">
         <v>103</v>
@@ -3262,7 +3247,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H26" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I26" t="s">
         <v>307</v>
@@ -3281,15 +3266,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>349</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>431</v>
+      <c r="C27" s="11" t="s">
+        <v>441</v>
       </c>
       <c r="D27" t="s">
         <v>104</v>
@@ -3305,7 +3290,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H27" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I27" t="s">
         <v>316</v>
@@ -3324,15 +3309,15 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>350</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>432</v>
+      <c r="C28" s="11" t="s">
+        <v>477</v>
       </c>
       <c r="D28" t="s">
         <v>105</v>
@@ -3348,7 +3333,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H28" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I28" t="s">
         <v>307</v>
@@ -3367,7 +3352,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3375,7 +3360,7 @@
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D29" t="s">
         <v>106</v>
@@ -3391,7 +3376,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H29" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I29" t="s">
         <v>310</v>
@@ -3410,7 +3395,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>352</v>
       </c>
@@ -3418,7 +3403,7 @@
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D30" t="s">
         <v>217</v>
@@ -3434,7 +3419,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H30" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I30" t="s">
         <v>317</v>
@@ -3454,15 +3439,15 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>353</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>435</v>
+      <c r="C31" s="11" t="s">
+        <v>470</v>
       </c>
       <c r="D31" t="s">
         <v>217</v>
@@ -3478,7 +3463,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H31" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I31" t="s">
         <v>317</v>
@@ -3497,7 +3482,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>354</v>
       </c>
@@ -3505,7 +3490,7 @@
         <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="D32" t="s">
         <v>107</v>
@@ -3521,7 +3506,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H32" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I32" t="s">
         <v>308</v>
@@ -3540,7 +3525,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>355</v>
       </c>
@@ -3548,7 +3533,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D33" t="s">
         <v>128</v>
@@ -3564,7 +3549,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H33" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I33" t="s">
         <v>318</v>
@@ -3584,7 +3569,7 @@
         <v>8.8000000000000009E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>356</v>
       </c>
@@ -3592,7 +3577,7 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D34" t="s">
         <v>128</v>
@@ -3608,7 +3593,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H34" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I34" t="s">
         <v>318</v>
@@ -3627,7 +3612,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -3635,7 +3620,7 @@
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D35" t="s">
         <v>108</v>
@@ -3651,7 +3636,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H35" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I35" t="s">
         <v>314</v>
@@ -3670,7 +3655,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>358</v>
       </c>
@@ -3678,7 +3663,7 @@
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -3694,7 +3679,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H36" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I36" t="s">
         <v>310</v>
@@ -3713,15 +3698,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>359</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>441</v>
+      <c r="C37" s="11" t="s">
+        <v>478</v>
       </c>
       <c r="D37" t="s">
         <v>110</v>
@@ -3737,7 +3722,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H37" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I37" t="s">
         <v>320</v>
@@ -3756,15 +3741,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>360</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>442</v>
+      <c r="C38" s="11" t="s">
+        <v>448</v>
       </c>
       <c r="D38" t="s">
         <v>111</v>
@@ -3780,7 +3765,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H38" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I38" t="s">
         <v>317</v>
@@ -3799,7 +3784,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>361</v>
       </c>
@@ -3807,7 +3792,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D39" t="s">
         <v>112</v>
@@ -3823,7 +3808,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H39" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I39" t="s">
         <v>310</v>
@@ -3842,7 +3827,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>362</v>
       </c>
@@ -3850,7 +3835,7 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D40" t="s">
         <v>113</v>
@@ -3866,7 +3851,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H40" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I40" t="s">
         <v>309</v>
@@ -3885,7 +3870,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>363</v>
       </c>
@@ -3893,7 +3878,7 @@
         <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D41" t="s">
         <v>114</v>
@@ -3909,7 +3894,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H41" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I41" t="s">
         <v>321</v>
@@ -3936,7 +3921,7 @@
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D42" t="s">
         <v>84</v>
@@ -3952,7 +3937,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H42" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I42" t="s">
         <v>308</v>
@@ -3980,7 +3965,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D43" t="s">
         <v>84</v>
@@ -3996,7 +3981,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H43" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I43" t="s">
         <v>308</v>
@@ -4015,7 +4000,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>366</v>
       </c>
@@ -4023,7 +4008,7 @@
         <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4054,7 +4039,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>367</v>
       </c>
@@ -4062,7 +4047,7 @@
         <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="D45" t="s">
         <v>116</v>
@@ -4093,7 +4078,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>368</v>
       </c>
@@ -4101,7 +4086,7 @@
         <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="D46" t="s">
         <v>117</v>
@@ -4132,7 +4117,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>369</v>
       </c>
@@ -4140,7 +4125,7 @@
         <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="D47" t="s">
         <v>118</v>
@@ -4171,7 +4156,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>370</v>
       </c>
@@ -4179,7 +4164,7 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="D48" t="s">
         <v>119</v>
@@ -4210,7 +4195,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>371</v>
       </c>
@@ -4218,7 +4203,7 @@
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="D49" t="s">
         <v>120</v>
@@ -4249,7 +4234,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>372</v>
       </c>
@@ -4257,7 +4242,7 @@
         <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="D50" t="s">
         <v>121</v>
@@ -4288,7 +4273,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>373</v>
       </c>
@@ -4296,7 +4281,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="D51" t="s">
         <v>92</v>
@@ -4312,7 +4297,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H51" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I51" t="str">
         <f>+_xlfn.XLOOKUP($D51,$D$11:$D$43,I$11:I$43,"missing",0)</f>
@@ -4334,15 +4319,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>374</v>
       </c>
       <c r="B52" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>456</v>
+      <c r="C52" s="11" t="s">
+        <v>479</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
@@ -4358,7 +4343,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H52" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I52" t="str">
         <f t="shared" si="1"/>
@@ -4380,7 +4365,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>375</v>
       </c>
@@ -4388,7 +4373,7 @@
         <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D53" t="s">
         <v>127</v>
@@ -4404,7 +4389,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H53" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I53" t="str">
         <f t="shared" si="1"/>
@@ -4427,7 +4412,7 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>376</v>
       </c>
@@ -4435,7 +4420,7 @@
         <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D54" t="s">
         <v>127</v>
@@ -4451,7 +4436,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H54" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="1"/>
@@ -4473,15 +4458,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>377</v>
       </c>
       <c r="B55" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>459</v>
+      <c r="C55" s="11" t="s">
+        <v>480</v>
       </c>
       <c r="D55" t="s">
         <v>96</v>
@@ -4497,7 +4482,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H55" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="1"/>
@@ -4519,15 +4504,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>378</v>
       </c>
       <c r="B56" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>460</v>
+      <c r="C56" s="11" t="s">
+        <v>481</v>
       </c>
       <c r="D56" t="s">
         <v>97</v>
@@ -4543,7 +4528,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H56" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I56" t="str">
         <f t="shared" si="1"/>
@@ -4565,15 +4550,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>379</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>461</v>
+      <c r="C57" s="11" t="s">
+        <v>482</v>
       </c>
       <c r="D57" t="s">
         <v>98</v>
@@ -4589,7 +4574,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H57" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="1"/>
@@ -4611,7 +4596,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>380</v>
       </c>
@@ -4619,7 +4604,7 @@
         <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D58" t="s">
         <v>99</v>
@@ -4635,7 +4620,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H58" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="1"/>
@@ -4657,7 +4642,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>381</v>
       </c>
@@ -4665,7 +4650,7 @@
         <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="D59" t="s">
         <v>100</v>
@@ -4681,7 +4666,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H59" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I59" t="str">
         <f t="shared" si="1"/>
@@ -4703,15 +4688,15 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>382</v>
       </c>
       <c r="B60" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>464</v>
+      <c r="C60" s="11" t="s">
+        <v>469</v>
       </c>
       <c r="D60" t="s">
         <v>101</v>
@@ -4727,7 +4712,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H60" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I60" t="str">
         <f t="shared" si="1"/>
@@ -4749,15 +4734,15 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>383</v>
       </c>
       <c r="B61" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>465</v>
+      <c r="C61" s="11" t="s">
+        <v>457</v>
       </c>
       <c r="D61" t="s">
         <v>138</v>
@@ -4773,7 +4758,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H61" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I61" t="str">
         <f t="shared" si="1"/>
@@ -4796,15 +4781,15 @@
         <v>0.33440000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>384</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>466</v>
+      <c r="C62" s="11" t="s">
+        <v>457</v>
       </c>
       <c r="D62" t="s">
         <v>138</v>
@@ -4820,7 +4805,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H62" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I62" t="str">
         <f t="shared" si="1"/>
@@ -4842,15 +4827,15 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>385</v>
       </c>
       <c r="B63" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>467</v>
+      <c r="C63" s="11" t="s">
+        <v>483</v>
       </c>
       <c r="D63" t="s">
         <v>102</v>
@@ -4866,7 +4851,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H63" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I63" t="str">
         <f t="shared" si="1"/>
@@ -4888,15 +4873,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>386</v>
       </c>
       <c r="B64" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>468</v>
+      <c r="C64" s="11" t="s">
+        <v>484</v>
       </c>
       <c r="D64" t="s">
         <v>103</v>
@@ -4912,7 +4897,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H64" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I64" t="str">
         <f t="shared" si="1"/>
@@ -4934,15 +4919,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>387</v>
       </c>
       <c r="B65" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>469</v>
+      <c r="C65" s="11" t="s">
+        <v>485</v>
       </c>
       <c r="D65" t="s">
         <v>105</v>
@@ -4958,7 +4943,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H65" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I65" t="str">
         <f t="shared" si="1"/>
@@ -4980,15 +4965,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>388</v>
       </c>
       <c r="B66" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>470</v>
+      <c r="C66" s="11" t="s">
+        <v>458</v>
       </c>
       <c r="D66" t="s">
         <v>106</v>
@@ -5004,7 +4989,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H66" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I66" t="str">
         <f t="shared" si="1"/>
@@ -5026,15 +5011,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>389</v>
       </c>
       <c r="B67" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>471</v>
+      <c r="C67" s="11" t="s">
+        <v>459</v>
       </c>
       <c r="D67" t="s">
         <v>217</v>
@@ -5050,7 +5035,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H67" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I67" t="str">
         <f t="shared" si="1"/>
@@ -5073,15 +5058,15 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>390</v>
       </c>
       <c r="B68" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>472</v>
+      <c r="C68" s="11" t="s">
+        <v>459</v>
       </c>
       <c r="D68" t="s">
         <v>217</v>
@@ -5097,7 +5082,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H68" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I68" t="str">
         <f t="shared" si="2"/>
@@ -5119,7 +5104,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>391</v>
       </c>
@@ -5127,7 +5112,7 @@
         <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>473</v>
+        <v>427</v>
       </c>
       <c r="D69" t="s">
         <v>107</v>
@@ -5143,7 +5128,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H69" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I69" t="str">
         <f t="shared" si="2"/>
@@ -5165,15 +5150,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>392</v>
       </c>
       <c r="B70" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>474</v>
+      <c r="C70" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="D70" t="s">
         <v>128</v>
@@ -5189,7 +5174,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H70" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I70" t="str">
         <f t="shared" si="2"/>
@@ -5212,15 +5197,15 @@
         <v>8.8000000000000009E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>393</v>
       </c>
       <c r="B71" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>475</v>
+      <c r="C71" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="D71" t="s">
         <v>128</v>
@@ -5236,7 +5221,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H71" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="2"/>
@@ -5258,15 +5243,15 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>394</v>
       </c>
       <c r="B72" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>476</v>
+      <c r="C72" s="11" t="s">
+        <v>462</v>
       </c>
       <c r="D72" t="s">
         <v>108</v>
@@ -5282,7 +5267,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H72" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I72" t="str">
         <f t="shared" si="2"/>
@@ -5304,15 +5289,15 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>395</v>
       </c>
       <c r="B73" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>477</v>
+      <c r="C73" s="11" t="s">
+        <v>461</v>
       </c>
       <c r="D73" t="s">
         <v>109</v>
@@ -5328,7 +5313,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H73" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I73" t="str">
         <f t="shared" si="2"/>
@@ -5350,15 +5335,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>396</v>
       </c>
       <c r="B74" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>478</v>
+      <c r="C74" s="11" t="s">
+        <v>486</v>
       </c>
       <c r="D74" t="s">
         <v>110</v>
@@ -5374,7 +5359,7 @@
         <v>permanent_crop</v>
       </c>
       <c r="H74" t="s">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="I74" t="str">
         <f t="shared" si="2"/>
@@ -5396,15 +5381,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>397</v>
       </c>
       <c r="B75" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>479</v>
+      <c r="C75" s="11" t="s">
+        <v>463</v>
       </c>
       <c r="D75" t="s">
         <v>111</v>
@@ -5420,7 +5405,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H75" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I75" t="str">
         <f t="shared" si="2"/>
@@ -5442,15 +5427,15 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>398</v>
       </c>
       <c r="B76" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>480</v>
+      <c r="C76" s="11" t="s">
+        <v>464</v>
       </c>
       <c r="D76" t="s">
         <v>112</v>
@@ -5466,7 +5451,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H76" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I76" t="str">
         <f t="shared" si="2"/>
@@ -5488,7 +5473,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>399</v>
       </c>
@@ -5496,7 +5481,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
@@ -5512,7 +5497,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H77" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I77" t="str">
         <f t="shared" si="2"/>
@@ -5534,15 +5519,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>400</v>
       </c>
       <c r="B78" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>482</v>
+      <c r="C78" s="11" t="s">
+        <v>466</v>
       </c>
       <c r="D78" t="s">
         <v>114</v>
@@ -5558,7 +5543,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H78" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I78" t="str">
         <f t="shared" si="2"/>
@@ -5587,8 +5572,8 @@
       <c r="B79" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>483</v>
+      <c r="C79" s="11" t="s">
+        <v>467</v>
       </c>
       <c r="D79" t="s">
         <v>84</v>
@@ -5604,7 +5589,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H79" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I79" t="str">
         <f t="shared" si="2"/>
@@ -5634,8 +5619,8 @@
       <c r="B80" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>484</v>
+      <c r="C80" s="11" t="s">
+        <v>467</v>
       </c>
       <c r="D80" t="s">
         <v>84</v>
@@ -5651,7 +5636,7 @@
         <v>annual_crop</v>
       </c>
       <c r="H80" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I80" t="str">
         <f t="shared" si="2"/>
@@ -5673,7 +5658,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>403</v>
       </c>
@@ -5681,7 +5666,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>485</v>
+        <v>428</v>
       </c>
       <c r="D81" t="s">
         <v>82</v>

--- a/data/crops/lu_c_factor_inventory.xlsx
+++ b/data/crops/lu_c_factor_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{222691F9-9D3B-4F39-9C0E-A780B282291D}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{563EFAE6-9E1B-4F5C-A7AC-F25B3E3E032A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F9D02B0-B27B-4DAB-8C90-F4F799F4886A}"/>
   </bookViews>
@@ -1830,7 +1830,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}" name="foreground_occupation_file_index" displayName="foreground_occupation_file_index" ref="A1:M81" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}"/>
+  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Rainfed"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="annual_crop"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{705AD7F1-810F-4078-AF9D-E2A5540C1883}" uniqueName="1" name="file_name" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{058DBECE-D8A6-44ED-99FF-D660796ED3BB}" uniqueName="2" name="land_use" queryTableFieldId="2" dataDxfId="9"/>
@@ -2225,7 +2236,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -2264,7 +2275,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -2303,7 +2314,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -2342,7 +2353,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>327</v>
       </c>
@@ -2381,7 +2392,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>328</v>
       </c>
@@ -2420,7 +2431,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>329</v>
       </c>
@@ -2459,7 +2470,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>330</v>
       </c>
@@ -2498,7 +2509,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>331</v>
       </c>
@@ -2537,7 +2548,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>332</v>
       </c>
@@ -2576,7 +2587,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>333</v>
       </c>
@@ -2619,7 +2630,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>334</v>
       </c>
@@ -2662,7 +2673,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>335</v>
       </c>
@@ -2706,7 +2717,7 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>336</v>
       </c>
@@ -2749,7 +2760,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>337</v>
       </c>
@@ -2792,7 +2803,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>338</v>
       </c>
@@ -2835,7 +2846,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>339</v>
       </c>
@@ -2878,7 +2889,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>340</v>
       </c>
@@ -2921,7 +2932,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>341</v>
       </c>
@@ -2964,7 +2975,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>342</v>
       </c>
@@ -3007,7 +3018,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>343</v>
       </c>
@@ -3050,7 +3061,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>344</v>
       </c>
@@ -3093,7 +3104,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>345</v>
       </c>
@@ -3137,7 +3148,7 @@
         <v>0.33440000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>346</v>
       </c>
@@ -3180,7 +3191,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>347</v>
       </c>
@@ -3223,7 +3234,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>348</v>
       </c>
@@ -3266,7 +3277,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>349</v>
       </c>
@@ -3309,7 +3320,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>350</v>
       </c>
@@ -3352,7 +3363,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3395,7 +3406,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>352</v>
       </c>
@@ -3439,7 +3450,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>353</v>
       </c>
@@ -3482,7 +3493,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>354</v>
       </c>
@@ -3525,7 +3536,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>355</v>
       </c>
@@ -3569,7 +3580,7 @@
         <v>8.8000000000000009E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>356</v>
       </c>
@@ -3612,7 +3623,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -3655,7 +3666,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>358</v>
       </c>
@@ -3698,7 +3709,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>359</v>
       </c>
@@ -3741,7 +3752,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>360</v>
       </c>
@@ -3784,7 +3795,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>361</v>
       </c>
@@ -3827,7 +3838,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>362</v>
       </c>
@@ -3870,7 +3881,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>363</v>
       </c>
@@ -3913,7 +3924,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>364</v>
       </c>
@@ -3957,7 +3968,7 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>365</v>
       </c>
@@ -4000,7 +4011,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>366</v>
       </c>
@@ -4039,7 +4050,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>367</v>
       </c>
@@ -4078,7 +4089,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>368</v>
       </c>
@@ -4117,7 +4128,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>369</v>
       </c>
@@ -4156,7 +4167,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>370</v>
       </c>
@@ -4195,7 +4206,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>371</v>
       </c>
@@ -4234,7 +4245,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>372</v>
       </c>
@@ -4273,7 +4284,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>373</v>
       </c>
@@ -4319,7 +4330,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>374</v>
       </c>
@@ -4458,7 +4469,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>377</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>378</v>
       </c>
@@ -4550,7 +4561,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>379</v>
       </c>
@@ -4642,7 +4653,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>381</v>
       </c>
@@ -4827,7 +4838,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>385</v>
       </c>
@@ -4873,7 +4884,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>386</v>
       </c>
@@ -4919,7 +4930,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>387</v>
       </c>
@@ -5335,7 +5346,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>396</v>
       </c>
@@ -5658,7 +5669,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>403</v>
       </c>

--- a/data/crops/lu_c_factor_inventory.xlsx
+++ b/data/crops/lu_c_factor_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{563EFAE6-9E1B-4F5C-A7AC-F25B3E3E032A}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC116040-C229-451C-B55F-B06B2F63D667}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F9D02B0-B27B-4DAB-8C90-F4F799F4886A}"/>
   </bookViews>
@@ -1830,18 +1830,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}" name="foreground_occupation_file_index" displayName="foreground_occupation_file_index" ref="A1:M81" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Rainfed"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="annual_crop"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M81" xr:uid="{B91ACB39-A6C6-4049-8B69-94BB57FE429E}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{705AD7F1-810F-4078-AF9D-E2A5540C1883}" uniqueName="1" name="file_name" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{058DBECE-D8A6-44ED-99FF-D660796ED3BB}" uniqueName="2" name="land_use" queryTableFieldId="2" dataDxfId="9"/>
@@ -2236,7 +2225,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -2275,7 +2264,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -2314,7 +2303,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -2353,7 +2342,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>327</v>
       </c>
@@ -2392,7 +2381,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>328</v>
       </c>
@@ -2431,7 +2420,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>329</v>
       </c>
@@ -2470,7 +2459,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>330</v>
       </c>
@@ -2509,7 +2498,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>331</v>
       </c>
@@ -2548,7 +2537,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>332</v>
       </c>
@@ -2587,7 +2576,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>333</v>
       </c>
@@ -2630,7 +2619,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>334</v>
       </c>
@@ -2673,7 +2662,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>335</v>
       </c>
@@ -2717,7 +2706,7 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>336</v>
       </c>
@@ -2760,7 +2749,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>337</v>
       </c>
@@ -2803,7 +2792,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>338</v>
       </c>
@@ -2846,7 +2835,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>339</v>
       </c>
@@ -2889,7 +2878,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>340</v>
       </c>
@@ -2932,7 +2921,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>341</v>
       </c>
@@ -2975,7 +2964,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>342</v>
       </c>
@@ -3018,7 +3007,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>343</v>
       </c>
@@ -3061,7 +3050,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>344</v>
       </c>
@@ -3104,7 +3093,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>345</v>
       </c>
@@ -3148,7 +3137,7 @@
         <v>0.33440000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>346</v>
       </c>
@@ -3191,7 +3180,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>347</v>
       </c>
@@ -3234,7 +3223,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>348</v>
       </c>
@@ -3277,7 +3266,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>349</v>
       </c>
@@ -3320,7 +3309,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>350</v>
       </c>
@@ -3363,7 +3352,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3406,7 +3395,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>352</v>
       </c>
@@ -3450,7 +3439,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>353</v>
       </c>
@@ -3493,7 +3482,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>354</v>
       </c>
@@ -3536,7 +3525,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>355</v>
       </c>
@@ -3580,7 +3569,7 @@
         <v>8.8000000000000009E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>356</v>
       </c>
@@ -3623,7 +3612,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -3666,7 +3655,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>358</v>
       </c>
@@ -3709,7 +3698,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>359</v>
       </c>
@@ -3752,7 +3741,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>360</v>
       </c>
@@ -3795,7 +3784,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>361</v>
       </c>
@@ -3838,7 +3827,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>362</v>
       </c>
@@ -3881,7 +3870,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>363</v>
       </c>
@@ -3924,7 +3913,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>364</v>
       </c>
@@ -3968,7 +3957,7 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>365</v>
       </c>
@@ -4011,7 +4000,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>366</v>
       </c>
@@ -4050,7 +4039,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>367</v>
       </c>
@@ -4089,7 +4078,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>368</v>
       </c>
@@ -4128,7 +4117,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>369</v>
       </c>
@@ -4167,7 +4156,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>370</v>
       </c>
@@ -4206,7 +4195,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>371</v>
       </c>
@@ -4245,7 +4234,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>372</v>
       </c>
@@ -4284,7 +4273,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>373</v>
       </c>
@@ -4330,7 +4319,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>374</v>
       </c>
@@ -4469,7 +4458,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>377</v>
       </c>
@@ -4515,7 +4504,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>378</v>
       </c>
@@ -4561,7 +4550,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>379</v>
       </c>
@@ -4653,7 +4642,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>381</v>
       </c>
@@ -4838,7 +4827,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>385</v>
       </c>
@@ -4884,7 +4873,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>386</v>
       </c>
@@ -4930,7 +4919,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>387</v>
       </c>
@@ -5346,7 +5335,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>396</v>
       </c>
@@ -5669,7 +5658,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>403</v>
       </c>

--- a/data/crops/lu_c_factor_inventory.xlsx
+++ b/data/crops/lu_c_factor_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC116040-C229-451C-B55F-B06B2F63D667}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="8_{AA2EB21E-9C36-413E-A92A-3D12D76AAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5721246-14B3-4A99-B1EB-AC12F47ADEC9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F9D02B0-B27B-4DAB-8C90-F4F799F4886A}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="486">
   <si>
     <t>file_name</t>
   </si>
@@ -1435,9 +1435,6 @@
   </si>
   <si>
     <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Tomato_irr.tif</t>
-  </si>
-  <si>
-    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_ron.tif</t>
   </si>
   <si>
     <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_roff.tif</t>
@@ -2627,7 +2624,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -2843,7 +2840,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2886,7 +2883,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -2929,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -3058,7 +3055,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -3188,7 +3185,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D25" t="s">
         <v>102</v>
@@ -3231,7 +3228,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D26" t="s">
         <v>103</v>
@@ -3317,7 +3314,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D28" t="s">
         <v>105</v>
@@ -3447,7 +3444,7 @@
         <v>32</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D31" t="s">
         <v>217</v>
@@ -3706,7 +3703,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D37" t="s">
         <v>110</v>
@@ -3965,7 +3962,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D43" t="s">
         <v>84</v>
@@ -4327,7 +4324,7 @@
         <v>53</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
@@ -4373,7 +4370,7 @@
         <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D53" t="s">
         <v>127</v>
@@ -4420,7 +4417,7 @@
         <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D54" t="s">
         <v>127</v>
@@ -4466,7 +4463,7 @@
         <v>56</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D55" t="s">
         <v>96</v>
@@ -4512,7 +4509,7 @@
         <v>57</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D56" t="s">
         <v>97</v>
@@ -4558,7 +4555,7 @@
         <v>58</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D57" t="s">
         <v>98</v>
@@ -4604,7 +4601,7 @@
         <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D58" t="s">
         <v>99</v>
@@ -4696,7 +4693,7 @@
         <v>61</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D60" t="s">
         <v>101</v>
@@ -4742,7 +4739,7 @@
         <v>62</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D61" t="s">
         <v>138</v>
@@ -4789,7 +4786,7 @@
         <v>63</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D62" t="s">
         <v>138</v>
@@ -4835,7 +4832,7 @@
         <v>64</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D63" t="s">
         <v>102</v>
@@ -4881,7 +4878,7 @@
         <v>65</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D64" t="s">
         <v>103</v>
@@ -4927,7 +4924,7 @@
         <v>66</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D65" t="s">
         <v>105</v>
@@ -4973,7 +4970,7 @@
         <v>67</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D66" t="s">
         <v>106</v>
@@ -5019,7 +5016,7 @@
         <v>68</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D67" t="s">
         <v>217</v>
@@ -5066,7 +5063,7 @@
         <v>69</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D68" t="s">
         <v>217</v>
@@ -5158,7 +5155,7 @@
         <v>71</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D70" t="s">
         <v>128</v>
@@ -5205,7 +5202,7 @@
         <v>72</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D71" t="s">
         <v>128</v>
@@ -5251,7 +5248,7 @@
         <v>73</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D72" t="s">
         <v>108</v>
@@ -5297,7 +5294,7 @@
         <v>74</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D73" t="s">
         <v>109</v>
@@ -5343,7 +5340,7 @@
         <v>75</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D74" t="s">
         <v>110</v>
@@ -5389,7 +5386,7 @@
         <v>76</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D75" t="s">
         <v>111</v>
@@ -5435,7 +5432,7 @@
         <v>77</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D76" t="s">
         <v>112</v>
@@ -5481,7 +5478,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
@@ -5527,7 +5524,7 @@
         <v>79</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D78" t="s">
         <v>114</v>
@@ -5573,7 +5570,7 @@
         <v>80</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D79" t="s">
         <v>84</v>
@@ -5620,7 +5617,7 @@
         <v>81</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D80" t="s">
         <v>84</v>
@@ -5698,8 +5695,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
